--- a/przyklady/wynik/Wniosek_SLO_Wróbel_Ignacy.xlsx
+++ b/przyklady/wynik/Wniosek_SLO_Wróbel_Ignacy.xlsx
@@ -722,8 +722,8 @@
   <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4.857142857142857" customWidth="1" min="1" max="1"/>
-    <col width="4.857142857142857" customWidth="1" min="2" max="2"/>
+    <col width="5.714285714285714" customWidth="1" min="1" max="1"/>
+    <col width="10.57142857142857" customWidth="1" min="2" max="2"/>
     <col width="35.71428571428572" customWidth="1" min="3" max="3"/>
     <col width="8.571428571428571" customWidth="1" min="4" max="4"/>
     <col width="8.571428571428571" customWidth="1" min="5" max="5"/>
